--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{08783B16-1D2E-4003-A615-1B8FD7A14BA0}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{3A7A0BA0-EAEA-47B6-B973-87355AF40E0F}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11868" activeTab="1" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11868" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -49,9 +49,6 @@
     <t>Title__c</t>
   </si>
   <si>
-    <t>Automation Site Visit</t>
-  </si>
-  <si>
     <t>Lookup</t>
   </si>
   <si>
@@ -113,6 +110,9 @@
   </si>
   <si>
     <t>TextArea</t>
+  </si>
+  <si>
+    <t>Automation Site Visit 1</t>
   </si>
 </sst>
 </file>
@@ -473,6 +473,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="18.21875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
@@ -499,7 +502,7 @@
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -507,13 +510,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -521,13 +524,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -562,13 +565,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="D2" s="1">
         <v>10</v>
@@ -576,13 +579,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="C3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1">
         <v>20</v>
@@ -590,72 +593,72 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{3A7A0BA0-EAEA-47B6-B973-87355AF40E0F}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{84ED97D8-5027-4942-8D13-694EE2E71921}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11868" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11868" activeTab="2" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
-    <sheet name="Edition" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
+    <sheet name="Edition" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -471,65 +472,53 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -539,125 +528,165 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B5" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="1">
+      <c r="C2" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="1">
+      <c r="C3" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="1" t="s">
         <v>19</v>
       </c>
     </row>

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="19126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{84ED97D8-5027-4942-8D13-694EE2E71921}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6495DCF3-4102-44A5-92F9-145ACA923C3F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11868" activeTab="2" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11868" activeTab="3" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
     <sheet name="Edition" sheetId="3" r:id="rId3"/>
+    <sheet name="Form Fields" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="29">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -693,4 +694,30 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6495DCF3-4102-44A5-92F9-145ACA923C3F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DEB1E7-4FD2-437B-A584-8DBE823003D1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11868" activeTab="3" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="47">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -114,7 +114,61 @@
     <t>TextArea</t>
   </si>
   <si>
-    <t>Automation Site Visit 1</t>
+    <t>Automation Site Visit Regression</t>
+  </si>
+  <si>
+    <t>SvProgramFormQ1__c</t>
+  </si>
+  <si>
+    <t>the organization have current written program policies and procedures</t>
+  </si>
+  <si>
+    <t>SvProgramFormQ2__c</t>
+  </si>
+  <si>
+    <t>the applicant have a current organization chart</t>
+  </si>
+  <si>
+    <t>SvProgramFormQ3__c</t>
+  </si>
+  <si>
+    <t>the organization have adequate accounting and financial systems in place for grant management</t>
+  </si>
+  <si>
+    <t>SvProgramFormQ4__c</t>
+  </si>
+  <si>
+    <t>the organization will have shared costs, has a cost allocation plan been provided</t>
+  </si>
+  <si>
+    <t>SvProgramFormQ5__c</t>
+  </si>
+  <si>
+    <t>the organization has indirect costs, was an indirect cost agreement submitted, or are they using the 10% de minimis rate</t>
+  </si>
+  <si>
+    <t>SvProgramFormQ6__c</t>
+  </si>
+  <si>
+    <t>facilities adequate for the grant program activities?  If not, provide an explanation</t>
+  </si>
+  <si>
+    <t>SvProgramFormQ7__c</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> all equipment items adequate for the planned grant program activities? If not, provide an explanatio</t>
+  </si>
+  <si>
+    <t>SvProgramFormQ8__c</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> the organization provided position descriptions for all grant-funded personnel</t>
+  </si>
+  <si>
+    <t>SvProgramFormQ9__c</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> hiring is to occur, does the agency adhere to Federal and State EEOC (Equal employment Opportunity Act) policies and procedures</t>
   </si>
 </sst>
 </file>
@@ -476,7 +530,8 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -698,12 +753,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.5546875" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="100.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -717,6 +772,105 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DEB1E7-4FD2-437B-A584-8DBE823003D1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ACB6177-7C6C-435B-9653-824DBB2F6962}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11868" activeTab="3" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -114,9 +114,6 @@
     <t>TextArea</t>
   </si>
   <si>
-    <t>Automation Site Visit Regression</t>
-  </si>
-  <si>
     <t>SvProgramFormQ1__c</t>
   </si>
   <si>
@@ -169,6 +166,9 @@
   </si>
   <si>
     <t xml:space="preserve"> hiring is to occur, does the agency adhere to Federal and State EEOC (Equal employment Opportunity Act) policies and procedures</t>
+  </si>
+  <si>
+    <t>Automation Site Visit Feb22</t>
   </si>
 </sst>
 </file>
@@ -553,7 +553,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -777,10 +777,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
         <v>29</v>
-      </c>
-      <c r="C2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -788,10 +788,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
         <v>31</v>
-      </c>
-      <c r="C3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -799,10 +799,10 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
         <v>33</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -810,10 +810,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
         <v>35</v>
-      </c>
-      <c r="C5" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -821,10 +821,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
         <v>37</v>
-      </c>
-      <c r="C6" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -832,10 +832,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
         <v>39</v>
-      </c>
-      <c r="C7" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -843,10 +843,10 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
         <v>41</v>
-      </c>
-      <c r="C8" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -854,10 +854,10 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" t="s">
         <v>43</v>
-      </c>
-      <c r="C9" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -865,10 +865,10 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
         <v>45</v>
-      </c>
-      <c r="C10" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ACB6177-7C6C-435B-9653-824DBB2F6962}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F90914-5228-4593-A760-42EDD5E23117}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
@@ -168,7 +168,7 @@
     <t xml:space="preserve"> hiring is to occur, does the agency adhere to Federal and State EEOC (Equal employment Opportunity Act) policies and procedures</t>
   </si>
   <si>
-    <t>Automation Site Visit Feb22</t>
+    <t xml:space="preserve">Automation Site Visit </t>
   </si>
 </sst>
 </file>

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F90914-5228-4593-A760-42EDD5E23117}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8E149A5-8A99-460D-A959-E2D15E649358}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="6" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
-    <sheet name="Edition" sheetId="3" r:id="rId3"/>
-    <sheet name="Form Fields" sheetId="5" r:id="rId4"/>
+    <sheet name="Outcomes" sheetId="6" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId4"/>
+    <sheet name="Edition" sheetId="3" r:id="rId5"/>
+    <sheet name="Form Fields1" sheetId="5" r:id="rId6"/>
+    <sheet name="Form Fields" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -28,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="108">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -117,71 +120,265 @@
     <t>SvProgramFormQ1__c</t>
   </si>
   <si>
-    <t>the organization have current written program policies and procedures</t>
-  </si>
-  <si>
     <t>SvProgramFormQ2__c</t>
   </si>
   <si>
-    <t>the applicant have a current organization chart</t>
-  </si>
-  <si>
     <t>SvProgramFormQ3__c</t>
   </si>
   <si>
-    <t>the organization have adequate accounting and financial systems in place for grant management</t>
-  </si>
-  <si>
     <t>SvProgramFormQ4__c</t>
   </si>
   <si>
-    <t>the organization will have shared costs, has a cost allocation plan been provided</t>
+    <t xml:space="preserve">Automation Site Visit </t>
+  </si>
+  <si>
+    <t>Reports and Outcomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Automation Finding</t>
+  </si>
+  <si>
+    <t>ActivityDescription__c</t>
+  </si>
+  <si>
+    <t>Automation Description</t>
+  </si>
+  <si>
+    <t>Type__c</t>
+  </si>
+  <si>
+    <t>Finding</t>
+  </si>
+  <si>
+    <t>Status__c</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>SvFinancialFormQ1__c</t>
+  </si>
+  <si>
+    <t>all requested financial reports and documentation been provided?  If not, what reports have not been provided</t>
+  </si>
+  <si>
+    <t>SvFinancialFormQ2__c</t>
+  </si>
+  <si>
+    <t>overall spending reflective of the original budget?  What is the current burn ratio</t>
+  </si>
+  <si>
+    <t>SvFinancialFormQ3__c</t>
+  </si>
+  <si>
+    <t>the project meet the budget time frame?  If not, provide an explanation</t>
+  </si>
+  <si>
+    <t>SvFinancialFormQ4__c</t>
+  </si>
+  <si>
+    <t>budget adjustments/amendments been needed?  If so, provide an explanation</t>
+  </si>
+  <si>
+    <t>SvFinancialFormQ5__c</t>
+  </si>
+  <si>
+    <t>match requirements being met?  If not, provide an explanation</t>
+  </si>
+  <si>
+    <t>SvFinancialFormQ6__c</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> the Chart of Accounts show segregation of grant programs</t>
+  </si>
+  <si>
+    <t>SvFinancialFormQ7__c</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> the agency has shared costs, has a cost allocation plan been provided</t>
+  </si>
+  <si>
+    <t>SvFinancialFormQ8__c</t>
+  </si>
+  <si>
+    <t>the agency has indirect costs, was an indirect cost agreement submitted, or are they using the 10% de minimus rate</t>
+  </si>
+  <si>
+    <t>SvFinancialFormQ9__c</t>
+  </si>
+  <si>
+    <t>the agency report grant expenditures on a cash or accrual basis of accounting</t>
+  </si>
+  <si>
+    <t>SvFinancialFormQ10__c</t>
+  </si>
+  <si>
+    <t>personnel costs properly posted to the general ledger</t>
+  </si>
+  <si>
+    <t>SvFinancialFormQ11__c</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> all employees and/or positions included in the current budget and identified in the budget justification</t>
+  </si>
+  <si>
+    <t>SvFinancialFormQ12__c</t>
+  </si>
+  <si>
+    <t>time sheets, activity reports, or payroll files available for review</t>
+  </si>
+  <si>
+    <t>SvFinancialFormQ13__c</t>
+  </si>
+  <si>
+    <t>fringe benefits reasonable, allocable, and allowable to the award</t>
+  </si>
+  <si>
+    <t>SvFinancialFormQ14__c</t>
+  </si>
+  <si>
+    <t>travel costs charged to the grant(s)</t>
+  </si>
+  <si>
+    <t>SvFinancialFormQ15__c</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> the supporting travel documentation able to be traced to the general ledger</t>
+  </si>
+  <si>
+    <t>SvFinancialFormQ16__c</t>
+  </si>
+  <si>
+    <t>on the supporting travel documentation, is the subrecipient reimbursing mileage in accordance to the Federal and State policies</t>
+  </si>
+  <si>
+    <t>SvFinancialFormQ17__c</t>
+  </si>
+  <si>
+    <t>rent being charged to the grant(s)</t>
+  </si>
+  <si>
+    <t>SvFinancialFormQ18__c</t>
+  </si>
+  <si>
+    <t>Yes, does the agency maintain a written lease agreement</t>
+  </si>
+  <si>
+    <t>SvFinancialFormQ19__c</t>
+  </si>
+  <si>
+    <t>Yes, does the lease period cover the grant period</t>
+  </si>
+  <si>
+    <t>CheckListComment5__c</t>
+  </si>
+  <si>
+    <t>all line items that have been tracked to this category:</t>
+  </si>
+  <si>
+    <t>SvFinancialFormQ20__c</t>
+  </si>
+  <si>
+    <t>the agency charged equipment to the grant</t>
+  </si>
+  <si>
+    <t>SvFinancialFormQ21__c</t>
+  </si>
+  <si>
+    <t>the equipment purchase documentation able to be traced to the general ledger</t>
+  </si>
+  <si>
+    <t>SvFinancialFormQ22__c</t>
+  </si>
+  <si>
+    <t>agency maintain a current asset inventory list</t>
+  </si>
+  <si>
+    <t>SvFinancialFormQ24__c</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> all line items that have been tracked to this category:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> contract costs being charged to the grant(s)</t>
+  </si>
+  <si>
+    <t>the agency provided all valid contract agreements</t>
+  </si>
+  <si>
+    <t>any contract expenditures been charged to the grant prior to the contract being signed</t>
+  </si>
+  <si>
+    <t>all contract expenditures properly reflected in the expenditure report</t>
+  </si>
+  <si>
+    <t>CheckListComment50__c</t>
+  </si>
+  <si>
+    <t>1. Does the organization have current written program policies and procedures?</t>
+  </si>
+  <si>
+    <t>2. Does the applicant have a current organization chart?</t>
+  </si>
+  <si>
+    <t>3. Does the organization have adequate accounting and financial systems in place for grant management? </t>
+  </si>
+  <si>
+    <t>4. If the organization will have shared costs, has a cost allocation plan been provided?</t>
   </si>
   <si>
     <t>SvProgramFormQ5__c</t>
   </si>
   <si>
-    <t>the organization has indirect costs, was an indirect cost agreement submitted, or are they using the 10% de minimis rate</t>
+    <t>5. If the organization has indirect costs, was an indirect cost agreement submitted, or are they using the 10% de minimis rate?</t>
   </si>
   <si>
     <t>SvProgramFormQ6__c</t>
   </si>
   <si>
-    <t>facilities adequate for the grant program activities?  If not, provide an explanation</t>
+    <t>1. Are facilities adequate for the grant program activities?  If not, provide an explanation.</t>
   </si>
   <si>
     <t>SvProgramFormQ7__c</t>
   </si>
   <si>
-    <t xml:space="preserve"> all equipment items adequate for the planned grant program activities? If not, provide an explanatio</t>
+    <t>2. Are all equipment items adequate for the planned grant program activities? If not, provide an explanation.</t>
   </si>
   <si>
     <t>SvProgramFormQ8__c</t>
   </si>
   <si>
-    <t xml:space="preserve"> the organization provided position descriptions for all grant-funded personnel</t>
+    <t>1. Has the organization provided position descriptions for all grant-funded personnel?</t>
   </si>
   <si>
     <t>SvProgramFormQ9__c</t>
   </si>
   <si>
-    <t xml:space="preserve"> hiring is to occur, does the agency adhere to Federal and State EEOC (Equal employment Opportunity Act) policies and procedures</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Site Visit </t>
+    <t>2. If hiring is to occur, does the agency adhere to Federal and State EEOC (Equal employment Opportunity Act) policies and procedures?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF6D6D6D"/>
+      <name val="Helvetica"/>
     </font>
   </fonts>
   <fills count="2">
@@ -204,8 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -213,6 +409,8 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -535,46 +733,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>46</v>
+      <c r="C2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -584,6 +782,77 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D79F1E74-3E81-4D35-A66E-768A31821CE0}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -592,54 +861,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -648,7 +917,50 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2233F5ED-8740-43F6-9895-B674ACB6DEF9}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -659,90 +971,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>19</v>
       </c>
     </row>
@@ -751,124 +1063,468 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
+  <dimension ref="A1:C30"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC98D198-04E6-490A-B46B-512D2A0BE3E3}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="100.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
+      <c r="C5" s="4" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" t="s">
-        <v>37</v>
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" t="s">
-        <v>39</v>
+      <c r="A7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" t="s">
-        <v>41</v>
+      <c r="A8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" t="s">
-        <v>43</v>
+      <c r="A9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" t="s">
-        <v>45</v>
+      <c r="A10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8E149A5-8A99-460D-A959-E2D15E649358}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21FCA047-6CBA-4BAE-9708-BE03E9B27F42}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="6" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21FCA047-6CBA-4BAE-9708-BE03E9B27F42}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3EFD636-626B-441C-99D5-BCFFCFC44F41}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="6" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
@@ -376,9 +376,10 @@
       <family val="3"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FF6D6D6D"/>
-      <name val="Helvetica"/>
+      <sz val="7"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1409,11 +1410,11 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC98D198-04E6-490A-B46B-512D2A0BE3E3}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="91.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1429,105 +1430,109 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="1" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="1" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="1" t="s">
         <v>107</v>
       </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B13" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21601"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3EFD636-626B-441C-99D5-BCFFCFC44F41}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E54552E-2C3E-4371-A6C0-EDFA2B456CC9}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="6" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -84,36 +84,21 @@
     <t>VisitEndDateTime__c</t>
   </si>
   <si>
-    <t>Description__c</t>
-  </si>
-  <si>
     <t>RichText</t>
   </si>
   <si>
     <t>Automation Test description</t>
   </si>
   <si>
-    <t>Pointsdiscussedwithofficials__c</t>
-  </si>
-  <si>
-    <t>SiteVisitPurpose__c</t>
-  </si>
-  <si>
     <t>Dropdown</t>
   </si>
   <si>
     <t>Routine based on monitoring responsibilities</t>
   </si>
   <si>
-    <t>SourceSiteVisit__c</t>
-  </si>
-  <si>
     <t>To fulfill pass-through monitoring responsibilities</t>
   </si>
   <si>
-    <t>SupportingCommentsQuestion1__c</t>
-  </si>
-  <si>
     <t>TextArea</t>
   </si>
   <si>
@@ -355,6 +340,21 @@
   </si>
   <si>
     <t>2. If hiring is to occur, does the agency adhere to Federal and State EEOC (Equal employment Opportunity Act) policies and procedures?</t>
+  </si>
+  <si>
+    <t>fieldDescription__c</t>
+  </si>
+  <si>
+    <t>fieldPointsdiscussedwithofficials__c</t>
+  </si>
+  <si>
+    <t>fieldSiteVisitPurpose__c</t>
+  </si>
+  <si>
+    <t>fieldSourceSiteVisit__c</t>
+  </si>
+  <si>
+    <t>fieldSupportingCommentsQuestion1__c</t>
   </si>
 </sst>
 </file>
@@ -727,13 +727,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -744,7 +744,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -752,10 +752,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -766,7 +766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -785,14 +785,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D79F1E74-3E81-4D35-A66E-768A31821CE0}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -803,48 +803,48 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="C5" t="s">
         <v>35</v>
-      </c>
-      <c r="C3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -856,12 +856,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -869,7 +869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -877,7 +877,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -885,32 +885,32 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -921,39 +921,39 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2233F5ED-8740-43F6-9895-B674ACB6DEF9}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" t="s">
         <v>35</v>
-      </c>
-      <c r="C1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -964,14 +964,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -982,7 +982,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -993,7 +993,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1004,76 +1004,77 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1084,323 +1085,323 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
         <v>41</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C5" t="s">
         <v>43</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C6" t="s">
         <v>45</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C7" t="s">
         <v>47</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C8" t="s">
         <v>49</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C9" t="s">
         <v>51</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C10" t="s">
         <v>53</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C11" t="s">
         <v>55</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C12" t="s">
         <v>57</v>
       </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C13" t="s">
         <v>59</v>
       </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C14" t="s">
         <v>61</v>
       </c>
-      <c r="C12" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C15" t="s">
         <v>63</v>
       </c>
-      <c r="C13" t="s">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C16" t="s">
         <v>65</v>
       </c>
-      <c r="C14" t="s">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C17" t="s">
         <v>67</v>
       </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="C18" t="s">
         <v>69</v>
       </c>
-      <c r="C16" t="s">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C19" t="s">
         <v>71</v>
       </c>
-      <c r="C17" t="s">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C20" t="s">
         <v>73</v>
       </c>
-      <c r="C18" t="s">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="C21" t="s">
         <v>75</v>
       </c>
-      <c r="C19" t="s">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C22" t="s">
         <v>77</v>
       </c>
-      <c r="C20" t="s">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C23" t="s">
         <v>79</v>
       </c>
-      <c r="C21" t="s">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="C24" t="s">
         <v>81</v>
       </c>
-      <c r="C22" t="s">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="C25" t="s">
         <v>83</v>
       </c>
-      <c r="C23" t="s">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" t="s">
         <v>85</v>
       </c>
-      <c r="C24" t="s">
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" t="s">
         <v>87</v>
       </c>
-      <c r="C25" t="s">
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" t="s">
-        <v>29</v>
-      </c>
-      <c r="C27" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" t="s">
-        <v>30</v>
-      </c>
-      <c r="C28" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" t="s">
-        <v>93</v>
-      </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1411,14 +1412,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC98D198-04E6-490A-B46B-512D2A0BE3E3}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1429,106 +1430,106 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="1" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="1" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="1" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C7" s="1" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B13" s="4"/>
     </row>
   </sheetData>

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -1,25 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21629"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E54552E-2C3E-4371-A6C0-EDFA2B456CC9}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E13C3A-C5C7-434B-8B16-2647E968F0AB}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
-    <sheet name="Outcomes" sheetId="6" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="7" r:id="rId4"/>
-    <sheet name="Edition" sheetId="3" r:id="rId5"/>
-    <sheet name="Form Fields1" sheetId="5" r:id="rId6"/>
-    <sheet name="Form Fields" sheetId="8" r:id="rId7"/>
+    <sheet name="Creation1" sheetId="10" r:id="rId2"/>
+    <sheet name="Outcomes" sheetId="6" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId5"/>
+    <sheet name="Edition" sheetId="3" r:id="rId6"/>
+    <sheet name="Sheet3" sheetId="9" r:id="rId7"/>
+    <sheet name="Form Fields1" sheetId="5" r:id="rId8"/>
+    <sheet name="Form Fields" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -31,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="109">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -355,6 +357,9 @@
   </si>
   <si>
     <t>fieldSupportingCommentsQuestion1__c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Program </t>
   </si>
 </sst>
 </file>
@@ -727,13 +732,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -744,7 +749,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -755,7 +760,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -766,7 +771,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -783,16 +788,74 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F38FE0-E02C-4583-8E5B-5FC537096D3A}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D79F1E74-3E81-4D35-A66E-768A31821CE0}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -803,7 +866,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>28</v>
       </c>
@@ -814,7 +877,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>28</v>
       </c>
@@ -825,7 +888,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>28</v>
       </c>
@@ -836,7 +899,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>28</v>
       </c>
@@ -853,15 +916,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -869,7 +932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -877,7 +940,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -885,7 +948,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -893,67 +956,24 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>22</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2233F5ED-8740-43F6-9895-B674ACB6DEF9}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -962,16 +982,59 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2233F5ED-8740-43F6-9895-B674ACB6DEF9}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -982,7 +1045,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -993,7 +1056,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1004,7 +1067,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1015,7 +1078,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1026,7 +1089,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1037,7 +1100,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1048,7 +1111,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1065,16 +1128,25 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17F4D4A9-3A34-4259-AC25-4E874229397A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1085,7 +1157,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1096,7 +1168,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1107,7 +1179,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1118,7 +1190,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1129,7 +1201,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1140,7 +1212,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1151,7 +1223,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1162,7 +1234,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1173,7 +1245,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1184,7 +1256,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -1195,7 +1267,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1206,7 +1278,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1217,7 +1289,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -1228,7 +1300,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1239,7 +1311,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -1250,7 +1322,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -1261,7 +1333,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -1272,7 +1344,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1283,7 +1355,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1294,7 +1366,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -1305,7 +1377,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -1316,7 +1388,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1327,7 +1399,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1338,7 +1410,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1349,7 +1421,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1360,7 +1432,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -1371,7 +1443,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -1382,7 +1454,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -1393,7 +1465,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -1409,17 +1481,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC98D198-04E6-490A-B46B-512D2A0BE3E3}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1430,7 +1502,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1441,7 +1513,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1452,7 +1524,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1463,7 +1535,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1474,7 +1546,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1485,7 +1557,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1496,7 +1568,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1507,7 +1579,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1518,7 +1590,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -1529,7 +1601,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" s="4"/>
     </row>
   </sheetData>

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Product Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E13C3A-C5C7-434B-8B16-2647E968F0AB}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D854560-497F-4556-8A79-F8CE78517E7F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="7" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -19,9 +19,11 @@
     <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet2" sheetId="7" r:id="rId5"/>
     <sheet name="Edition" sheetId="3" r:id="rId6"/>
-    <sheet name="Sheet3" sheetId="9" r:id="rId7"/>
-    <sheet name="Form Fields1" sheetId="5" r:id="rId8"/>
-    <sheet name="Form Fields" sheetId="8" r:id="rId9"/>
+    <sheet name="SourceError" sheetId="11" r:id="rId7"/>
+    <sheet name="InstructionError" sheetId="12" r:id="rId8"/>
+    <sheet name="Sheet3" sheetId="9" r:id="rId9"/>
+    <sheet name="Form Fields1" sheetId="5" r:id="rId10"/>
+    <sheet name="Form Fields" sheetId="8" r:id="rId11"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="109">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -732,13 +734,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -749,7 +751,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -760,7 +762,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -771,7 +773,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -784,19 +786,492 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
+  <dimension ref="A1:C30"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" t="s">
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC98D198-04E6-490A-B46B-512D2A0BE3E3}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F38FE0-E02C-4583-8E5B-5FC537096D3A}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -807,7 +1282,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -818,7 +1293,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -829,7 +1304,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -848,14 +1323,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D79F1E74-3E81-4D35-A66E-768A31821CE0}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -866,7 +1341,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>28</v>
       </c>
@@ -877,7 +1352,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>28</v>
       </c>
@@ -888,7 +1363,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>28</v>
       </c>
@@ -899,7 +1374,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>28</v>
       </c>
@@ -919,12 +1394,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -932,7 +1407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -940,7 +1415,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -948,7 +1423,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -956,22 +1431,22 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>22</v>
       </c>
@@ -984,9 +1459,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2233F5ED-8740-43F6-9895-B674ACB6DEF9}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
@@ -997,7 +1472,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>28</v>
       </c>
@@ -1008,7 +1483,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
@@ -1027,14 +1502,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1045,7 +1520,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1056,7 +1531,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1067,7 +1542,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1078,7 +1553,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1089,7 +1564,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1100,7 +1575,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1111,7 +1586,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1129,24 +1604,106 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17F4D4A9-3A34-4259-AC25-4E874229397A}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939E4119-ACED-4858-8093-FD1B7FF9F1D3}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
-  <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E614565-35C2-477C-A727-DE66F54E56C3}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1157,323 +1714,70 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>106</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" t="s">
-        <v>80</v>
-      </c>
-      <c r="C24" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" t="s">
-        <v>82</v>
-      </c>
-      <c r="C25" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" t="s">
-        <v>25</v>
-      </c>
-      <c r="C28" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1482,130 +1786,10 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC98D198-04E6-490A-B46B-512D2A0BE3E3}">
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B13" s="4"/>
-    </row>
-  </sheetData>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17F4D4A9-3A34-4259-AC25-4E874229397A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Product Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D854560-497F-4556-8A79-F8CE78517E7F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9C8650-891E-49EE-BC3A-04BF685CBD91}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="7" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="110">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -362,6 +362,9 @@
   </si>
   <si>
     <t xml:space="preserve">Program </t>
+  </si>
+  <si>
+    <t>Automation spi</t>
   </si>
 </sst>
 </file>
@@ -770,7 +773,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9C8650-891E-49EE-BC3A-04BF685CBD91}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D29FBC96-C4B5-4E0C-B4F6-616562DA181F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="10" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="109">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -362,9 +362,6 @@
   </si>
   <si>
     <t xml:space="preserve">Program </t>
-  </si>
-  <si>
-    <t>Automation spi</t>
   </si>
 </sst>
 </file>
@@ -737,13 +734,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -754,7 +751,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -765,7 +762,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -773,10 +770,10 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -795,13 +792,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -812,7 +809,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -823,7 +820,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -834,7 +831,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -845,7 +842,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -856,7 +853,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -867,7 +864,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -878,7 +875,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -889,7 +886,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -900,7 +897,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -911,7 +908,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -922,7 +919,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -933,7 +930,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -944,7 +941,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -955,7 +952,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -966,7 +963,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -977,7 +974,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -988,7 +985,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -999,7 +996,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1010,7 +1007,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1021,7 +1018,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -1032,7 +1029,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -1043,7 +1040,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1054,7 +1051,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1065,7 +1062,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1076,7 +1073,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1087,7 +1084,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -1098,7 +1095,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -1109,7 +1106,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -1120,7 +1117,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -1139,14 +1136,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC98D198-04E6-490A-B46B-512D2A0BE3E3}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1157,7 +1154,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1168,7 +1165,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1179,7 +1176,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1190,7 +1187,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1201,7 +1198,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1212,7 +1209,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1223,7 +1220,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1234,7 +1231,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1245,7 +1242,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -1256,7 +1253,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" s="4"/>
     </row>
   </sheetData>
@@ -1268,13 +1265,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F38FE0-E02C-4583-8E5B-5FC537096D3A}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1285,7 +1282,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1296,7 +1293,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1307,7 +1304,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1326,14 +1323,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D79F1E74-3E81-4D35-A66E-768A31821CE0}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1344,7 +1341,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>28</v>
       </c>
@@ -1355,7 +1352,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>28</v>
       </c>
@@ -1366,7 +1363,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>28</v>
       </c>
@@ -1377,7 +1374,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>28</v>
       </c>
@@ -1397,12 +1394,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1410,7 +1407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1418,7 +1415,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1426,7 +1423,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1434,22 +1431,22 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>22</v>
       </c>
@@ -1462,9 +1459,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2233F5ED-8740-43F6-9895-B674ACB6DEF9}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
@@ -1475,7 +1472,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>28</v>
       </c>
@@ -1486,7 +1483,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
@@ -1505,14 +1502,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1523,7 +1520,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1534,7 +1531,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1545,7 +1542,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1556,7 +1553,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1567,7 +1564,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1578,7 +1575,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1589,7 +1586,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1609,13 +1606,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939E4119-ACED-4858-8093-FD1B7FF9F1D3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1626,7 +1623,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1637,7 +1634,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1648,7 +1645,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1659,7 +1656,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1670,7 +1667,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1681,7 +1678,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1700,13 +1697,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E614565-35C2-477C-A727-DE66F54E56C3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1717,7 +1714,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1728,7 +1725,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1739,7 +1736,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1750,7 +1747,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1761,7 +1758,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1772,7 +1769,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1791,7 +1788,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17F4D4A9-3A34-4259-AC25-4E874229397A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\Automation projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D29FBC96-C4B5-4E0C-B4F6-616562DA181F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D06C5EB3-710E-412F-A2EE-5904F7D80344}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="10" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" activeTab="1" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -118,9 +118,6 @@
     <t>SvProgramFormQ4__c</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation Site Visit </t>
-  </si>
-  <si>
     <t>Reports and Outcomes</t>
   </si>
   <si>
@@ -362,6 +359,9 @@
   </si>
   <si>
     <t xml:space="preserve">Program </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Runtime Site Visit </t>
   </si>
 </sst>
 </file>
@@ -734,13 +734,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.53515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -751,7 +751,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -759,10 +759,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -773,7 +773,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -792,13 +792,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.84375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.3046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -809,271 +809,271 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
         <v>36</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>38</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>40</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>42</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>44</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>46</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>48</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>50</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>52</v>
       </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>54</v>
       </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>56</v>
       </c>
-      <c r="C12" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>58</v>
       </c>
-      <c r="C13" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>60</v>
       </c>
-      <c r="C14" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>62</v>
       </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>64</v>
       </c>
-      <c r="C16" t="s">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>66</v>
       </c>
-      <c r="C17" t="s">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>68</v>
       </c>
-      <c r="C18" t="s">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>70</v>
       </c>
-      <c r="C19" t="s">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>72</v>
       </c>
-      <c r="C20" t="s">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>74</v>
       </c>
-      <c r="C21" t="s">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>76</v>
       </c>
-      <c r="C22" t="s">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>78</v>
       </c>
-      <c r="C23" t="s">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>80</v>
       </c>
-      <c r="C24" t="s">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>82</v>
       </c>
-      <c r="C25" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1081,10 +1081,10 @@
         <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -1092,10 +1092,10 @@
         <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -1103,10 +1103,10 @@
         <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -1114,18 +1114,18 @@
         <v>26</v>
       </c>
       <c r="C29" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" t="s">
-        <v>88</v>
-      </c>
       <c r="C30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1136,14 +1136,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC98D198-04E6-490A-B46B-512D2A0BE3E3}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.4609375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.3046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1154,7 +1154,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1162,10 +1162,10 @@
         <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1173,10 +1173,10 @@
         <v>24</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1184,10 +1184,10 @@
         <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1195,65 +1195,65 @@
         <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="1" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="1" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C9" s="1" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B13" s="4"/>
     </row>
   </sheetData>
@@ -1265,13 +1265,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F38FE0-E02C-4583-8E5B-5FC537096D3A}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.53515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1290,10 +1290,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1304,7 +1304,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1323,14 +1323,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D79F1E74-3E81-4D35-A66E-768A31821CE0}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.53515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1341,48 +1341,48 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" t="s">
         <v>30</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" t="s">
         <v>32</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" t="s">
         <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1394,12 +1394,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.53515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1407,7 +1407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1415,7 +1415,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1431,22 +1431,22 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
         <v>22</v>
       </c>
@@ -1459,39 +1459,39 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2233F5ED-8740-43F6-9895-B674ACB6DEF9}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" t="s">
         <v>30</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" t="s">
         <v>32</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" t="s">
         <v>34</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1502,14 +1502,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.3046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1531,7 +1531,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1542,56 +1542,56 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
@@ -1606,13 +1606,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939E4119-ACED-4858-8093-FD1B7FF9F1D3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.3046875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1645,45 +1645,45 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -1697,13 +1697,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E614565-35C2-477C-A727-DE66F54E56C3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.3046875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1714,7 +1714,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1736,45 +1736,45 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -1788,7 +1788,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17F4D4A9-3A34-4259-AC25-4E874229397A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\Automation projects\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D06C5EB3-710E-412F-A2EE-5904F7D80344}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A83DF90-6961-4B1F-8EB0-A538429D3564}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" activeTab="1" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="5304" yWindow="1500" windowWidth="17280" windowHeight="8964" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="110">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -361,14 +361,17 @@
     <t xml:space="preserve">Program </t>
   </si>
   <si>
-    <t xml:space="preserve">Automation Runtime Site Visit </t>
+    <t>Automation Award Runtime Site Visit"</t>
+  </si>
+  <si>
+    <t>Automation Award Runtime Site Visit</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -387,6 +390,13 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF297BDE"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -409,7 +419,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -419,6 +429,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -734,13 +747,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.53515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -751,18 +764,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C2" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -773,7 +786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -786,19 +799,20 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.84375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -809,7 +823,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -820,7 +834,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -831,7 +845,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -842,7 +856,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -853,7 +867,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -864,7 +878,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -875,7 +889,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -886,7 +900,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -897,7 +911,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -908,7 +922,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -919,7 +933,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -930,7 +944,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -941,7 +955,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -952,7 +966,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -963,7 +977,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -974,7 +988,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -985,7 +999,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -996,7 +1010,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1007,7 +1021,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1018,7 +1032,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -1029,7 +1043,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -1040,7 +1054,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1051,7 +1065,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1062,7 +1076,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1073,7 +1087,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1084,7 +1098,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -1095,7 +1109,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -1106,7 +1120,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -1117,7 +1131,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -1136,14 +1150,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC98D198-04E6-490A-B46B-512D2A0BE3E3}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.4609375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1154,7 +1168,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1165,7 +1179,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1176,7 +1190,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1187,7 +1201,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1198,7 +1212,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1209,7 +1223,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1220,7 +1234,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1231,7 +1245,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1242,7 +1256,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -1253,7 +1267,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" s="4"/>
     </row>
   </sheetData>
@@ -1265,13 +1279,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F38FE0-E02C-4583-8E5B-5FC537096D3A}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.53515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1282,18 +1296,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="5" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1304,7 +1318,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1317,20 +1331,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D79F1E74-3E81-4D35-A66E-768A31821CE0}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.53515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1341,7 +1356,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>27</v>
       </c>
@@ -1352,7 +1367,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>27</v>
       </c>
@@ -1363,7 +1378,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>27</v>
       </c>
@@ -1374,7 +1389,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>27</v>
       </c>
@@ -1394,12 +1409,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1407,7 +1422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1415,7 +1430,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1423,7 +1438,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1431,22 +1446,22 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>22</v>
       </c>
@@ -1459,9 +1474,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2233F5ED-8740-43F6-9895-B674ACB6DEF9}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>27</v>
       </c>
@@ -1472,7 +1487,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>27</v>
       </c>
@@ -1483,7 +1498,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
@@ -1502,14 +1517,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1520,7 +1535,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1531,7 +1546,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1542,7 +1557,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1553,7 +1568,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1564,7 +1579,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1575,7 +1590,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1586,7 +1601,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1606,13 +1621,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939E4119-ACED-4858-8093-FD1B7FF9F1D3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="37.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1623,7 +1638,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1634,7 +1649,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1645,7 +1660,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1656,7 +1671,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1667,7 +1682,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1678,7 +1693,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1697,13 +1712,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E614565-35C2-477C-A727-DE66F54E56C3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="37.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1714,7 +1729,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1725,7 +1740,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1736,7 +1751,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1747,7 +1762,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1758,7 +1773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1769,7 +1784,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1788,7 +1803,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17F4D4A9-3A34-4259-AC25-4E874229397A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\Automation projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A83DF90-6961-4B1F-8EB0-A538429D3564}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA479C98-91C2-411F-8124-A03BB6FCB803}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5304" yWindow="1500" windowWidth="17280" windowHeight="8964" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="109">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -361,10 +361,7 @@
     <t xml:space="preserve">Program </t>
   </si>
   <si>
-    <t>Automation Award Runtime Site Visit"</t>
-  </si>
-  <si>
-    <t>Automation Award Runtime Site Visit</t>
+    <t>Automation Runtime Award Site Visit"</t>
   </si>
 </sst>
 </file>
@@ -747,13 +744,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.53515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -764,7 +761,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -772,10 +769,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -786,7 +783,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -806,13 +803,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.84375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.3046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -823,7 +820,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -834,7 +831,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -845,7 +842,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -856,7 +853,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -867,7 +864,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -878,7 +875,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -889,7 +886,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -900,7 +897,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -911,7 +908,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -922,7 +919,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -933,7 +930,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -944,7 +941,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -955,7 +952,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -966,7 +963,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -977,7 +974,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -988,7 +985,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -999,7 +996,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -1010,7 +1007,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1021,7 +1018,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1032,7 +1029,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -1043,7 +1040,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -1054,7 +1051,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1065,7 +1062,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1076,7 +1073,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1087,7 +1084,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1098,7 +1095,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -1109,7 +1106,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -1120,7 +1117,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -1131,7 +1128,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -1150,14 +1147,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC98D198-04E6-490A-B46B-512D2A0BE3E3}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.4609375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.3046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1168,7 +1165,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1179,7 +1176,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1190,7 +1187,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1201,7 +1198,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1212,7 +1209,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1223,7 +1220,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1234,7 +1231,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1245,7 +1242,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1256,7 +1253,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -1267,7 +1264,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B13" s="4"/>
     </row>
   </sheetData>
@@ -1279,13 +1276,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F38FE0-E02C-4583-8E5B-5FC537096D3A}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.53515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1296,7 +1293,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1307,7 +1304,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1318,7 +1315,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1338,14 +1335,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D79F1E74-3E81-4D35-A66E-768A31821CE0}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.53515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1356,7 +1353,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
         <v>27</v>
       </c>
@@ -1367,7 +1364,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>27</v>
       </c>
@@ -1378,7 +1375,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
         <v>27</v>
       </c>
@@ -1389,7 +1386,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
         <v>27</v>
       </c>
@@ -1409,12 +1406,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.53515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1422,7 +1419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1430,7 +1427,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1438,7 +1435,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1446,22 +1443,22 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
         <v>22</v>
       </c>
@@ -1474,9 +1471,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2233F5ED-8740-43F6-9895-B674ACB6DEF9}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>27</v>
       </c>
@@ -1487,7 +1484,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>27</v>
       </c>
@@ -1498,7 +1495,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
@@ -1517,14 +1514,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.3046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1535,7 +1532,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1546,7 +1543,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1557,7 +1554,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1568,7 +1565,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1579,7 +1576,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1590,7 +1587,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1601,7 +1598,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1621,13 +1618,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939E4119-ACED-4858-8093-FD1B7FF9F1D3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.3046875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1638,7 +1635,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1649,7 +1646,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1660,7 +1657,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1671,7 +1668,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1682,7 +1679,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1693,7 +1690,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1712,13 +1709,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E614565-35C2-477C-A727-DE66F54E56C3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.3046875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1729,7 +1726,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1740,7 +1737,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1751,7 +1748,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1762,7 +1759,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1773,7 +1770,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1784,7 +1781,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1803,7 +1800,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17F4D4A9-3A34-4259-AC25-4E874229397A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\Automation projects\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA479C98-91C2-411F-8124-A03BB6FCB803}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8EB000D-384F-4C0B-ACDA-6CB6406A881F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="110">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -362,6 +362,9 @@
   </si>
   <si>
     <t>Automation Runtime Award Site Visit"</t>
+  </si>
+  <si>
+    <t>Automation SPI3</t>
   </si>
 </sst>
 </file>
@@ -744,13 +747,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="20.53515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.53125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -761,7 +764,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -772,7 +775,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -780,10 +783,10 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -803,13 +806,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="21.84375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -820,7 +823,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -831,7 +834,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -842,7 +845,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -853,7 +856,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -864,7 +867,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -875,7 +878,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -886,7 +889,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -897,7 +900,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -908,7 +911,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -919,7 +922,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -930,7 +933,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -941,7 +944,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -952,7 +955,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -963,7 +966,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -974,7 +977,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -985,7 +988,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -996,7 +999,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -1007,7 +1010,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1018,7 +1021,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1029,7 +1032,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -1040,7 +1043,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -1051,7 +1054,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1062,7 +1065,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1073,7 +1076,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1084,7 +1087,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1095,7 +1098,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -1106,7 +1109,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -1117,7 +1120,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -1128,7 +1131,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -1147,14 +1150,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC98D198-04E6-490A-B46B-512D2A0BE3E3}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="16.4609375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1165,7 +1168,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1176,7 +1179,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1187,7 +1190,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1198,7 +1201,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1209,7 +1212,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1220,7 +1223,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1231,7 +1234,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1242,7 +1245,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1253,7 +1256,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -1264,7 +1267,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B13" s="4"/>
     </row>
   </sheetData>
@@ -1276,13 +1279,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F38FE0-E02C-4583-8E5B-5FC537096D3A}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="20.53515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.53125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1293,7 +1296,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1304,7 +1307,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1315,7 +1318,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1335,14 +1338,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D79F1E74-3E81-4D35-A66E-768A31821CE0}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="19.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.53515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.53125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1353,7 +1356,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>27</v>
       </c>
@@ -1364,7 +1367,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>27</v>
       </c>
@@ -1375,7 +1378,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>27</v>
       </c>
@@ -1386,7 +1389,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>27</v>
       </c>
@@ -1406,12 +1409,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="9.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.53125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1419,7 +1422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1427,7 +1430,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1435,7 +1438,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1443,22 +1446,22 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>22</v>
       </c>
@@ -1471,9 +1474,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2233F5ED-8740-43F6-9895-B674ACB6DEF9}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>27</v>
       </c>
@@ -1484,7 +1487,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>27</v>
       </c>
@@ -1495,7 +1498,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
@@ -1514,14 +1517,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1532,7 +1535,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1543,7 +1546,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1554,7 +1557,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1565,7 +1568,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1576,7 +1579,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1587,7 +1590,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1598,7 +1601,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1618,13 +1621,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939E4119-ACED-4858-8093-FD1B7FF9F1D3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="37.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1635,7 +1638,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1646,7 +1649,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1657,7 +1660,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1668,7 +1671,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1679,7 +1682,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1690,7 +1693,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1709,13 +1712,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E614565-35C2-477C-A727-DE66F54E56C3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="37.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1726,7 +1729,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1737,7 +1740,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1748,7 +1751,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1759,7 +1762,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1770,7 +1773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1781,7 +1784,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1800,7 +1803,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17F4D4A9-3A34-4259-AC25-4E874229397A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8EB000D-384F-4C0B-ACDA-6CB6406A881F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2205E1DF-4520-49C5-836A-7318DFE07E5D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="111">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -365,6 +365,9 @@
   </si>
   <si>
     <t>Automation SPI3</t>
+  </si>
+  <si>
+    <t>Automation Runtime Award Site Visit</t>
   </si>
 </sst>
 </file>
@@ -750,7 +753,7 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="20.53125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
@@ -772,7 +775,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2205E1DF-4520-49C5-836A-7318DFE07E5D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05363EE0-E4DA-4D56-84E8-D3619DE019EB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -367,7 +367,7 @@
     <t>Automation SPI3</t>
   </si>
   <si>
-    <t>Automation Runtime Award Site Visit</t>
+    <t>Automation Runtime Site Visit</t>
   </si>
 </sst>
 </file>

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05363EE0-E4DA-4D56-84E8-D3619DE019EB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADAC9E5B-DE94-4427-A943-67A3EE0F91AE}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
@@ -1285,7 +1285,7 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="20.53125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADAC9E5B-DE94-4427-A943-67A3EE0F91AE}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7817E523-EA7A-4BFF-B156-AFD77A00D380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="113">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -368,13 +368,19 @@
   </si>
   <si>
     <t>Automation Runtime Site Visit</t>
+  </si>
+  <si>
+    <t>fieldVisitDateandTime__c</t>
+  </si>
+  <si>
+    <t>fieldVisitEndDateTime__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -401,6 +407,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF202124"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -422,7 +434,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -435,6 +447,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -750,13 +763,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.53125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -767,7 +780,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -778,7 +791,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -789,7 +802,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -809,13 +822,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.86328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -826,7 +839,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -837,7 +850,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -848,7 +861,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -859,7 +872,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -870,7 +883,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -881,7 +894,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -892,7 +905,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -903,7 +916,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -914,7 +927,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -925,7 +938,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -936,7 +949,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -947,7 +960,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -958,7 +971,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -969,7 +982,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -980,7 +993,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -991,7 +1004,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -1002,7 +1015,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -1013,7 +1026,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1024,7 +1037,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1035,7 +1048,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -1046,7 +1059,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -1057,7 +1070,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1068,7 +1081,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1079,7 +1092,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1090,7 +1103,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1101,7 +1114,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -1112,7 +1125,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -1123,7 +1136,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -1134,7 +1147,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -1153,14 +1166,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC98D198-04E6-490A-B46B-512D2A0BE3E3}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1171,7 +1184,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1182,7 +1195,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1193,7 +1206,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1204,7 +1217,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -1215,7 +1228,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1226,7 +1239,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -1237,7 +1250,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -1248,7 +1261,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1259,7 +1272,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -1270,7 +1283,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B13" s="4"/>
     </row>
   </sheetData>
@@ -1282,13 +1295,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F38FE0-E02C-4583-8E5B-5FC537096D3A}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.53125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1299,7 +1312,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1310,7 +1323,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1321,7 +1334,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1341,14 +1354,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D79F1E74-3E81-4D35-A66E-768A31821CE0}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.53125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1359,7 +1372,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>27</v>
       </c>
@@ -1370,7 +1383,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>27</v>
       </c>
@@ -1381,7 +1394,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>27</v>
       </c>
@@ -1392,7 +1405,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>27</v>
       </c>
@@ -1412,12 +1425,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC7A54C-E16D-458B-92CE-DB4DE5E21708}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.53125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1425,7 +1438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1433,7 +1446,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1441,7 +1454,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1449,22 +1462,22 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>22</v>
       </c>
@@ -1477,9 +1490,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2233F5ED-8740-43F6-9895-B674ACB6DEF9}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>27</v>
       </c>
@@ -1490,7 +1503,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>27</v>
       </c>
@@ -1501,7 +1514,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
@@ -1520,14 +1533,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1538,29 +1551,29 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
-        <v>15</v>
+      <c r="B2" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
-        <v>16</v>
+      <c r="B3" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="C3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1571,7 +1584,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1582,7 +1595,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1593,7 +1606,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1604,7 +1617,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1624,13 +1637,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939E4119-ACED-4858-8093-FD1B7FF9F1D3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1641,7 +1654,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1652,7 +1665,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1663,7 +1676,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1674,7 +1687,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1685,7 +1698,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1696,7 +1709,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1715,13 +1728,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E614565-35C2-477C-A727-DE66F54E56C3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1732,7 +1745,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1743,7 +1756,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1754,7 +1767,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1765,7 +1778,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1776,7 +1789,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1787,7 +1800,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1806,7 +1819,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17F4D4A9-3A34-4259-AC25-4E874229397A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7817E523-EA7A-4BFF-B156-AFD77A00D380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF9C0062-D4E0-485E-A371-22E5133E5008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="6" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="111">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -80,12 +80,6 @@
   </si>
   <si>
     <t>Date</t>
-  </si>
-  <si>
-    <t>VisitDateandTime__c</t>
-  </si>
-  <si>
-    <t>VisitEndDateTime__c</t>
   </si>
   <si>
     <t>RichText</t>
@@ -788,7 +782,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -799,7 +793,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -844,10 +838,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -855,10 +849,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -866,10 +860,10 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -877,10 +871,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -888,10 +882,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -899,10 +893,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -910,10 +904,10 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -921,10 +915,10 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -932,10 +926,10 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -943,10 +937,10 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -954,10 +948,10 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -965,10 +959,10 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -976,10 +970,10 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -987,10 +981,10 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -998,10 +992,10 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1009,10 +1003,10 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1020,10 +1014,10 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -1031,10 +1025,10 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1042,10 +1036,10 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1053,10 +1047,10 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1064,10 +1058,10 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1075,10 +1069,10 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -1086,10 +1080,10 @@
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1097,10 +1091,10 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1108,10 +1102,10 @@
         <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1119,10 +1113,10 @@
         <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C27" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -1130,10 +1124,10 @@
         <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C28" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -1141,10 +1135,10 @@
         <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C29" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1152,10 +1146,10 @@
         <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C30" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1189,10 +1183,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1200,10 +1194,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1211,10 +1205,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1222,10 +1216,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1233,10 +1227,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1244,10 +1238,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1255,10 +1249,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1266,10 +1260,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1277,10 +1271,10 @@
         <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1320,7 +1314,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1342,7 +1336,7 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1374,46 +1368,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1459,27 +1453,27 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1494,35 +1488,35 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="C1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1556,7 +1550,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -1567,7 +1561,7 @@
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -1578,10 +1572,10 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1589,10 +1583,10 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1600,10 +1594,10 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1611,10 +1605,10 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1622,10 +1616,10 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1658,8 +1652,8 @@
       <c r="A2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
-        <v>15</v>
+      <c r="B2" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -1669,8 +1663,8 @@
       <c r="A3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
-        <v>16</v>
+      <c r="B3" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -1681,10 +1675,10 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1692,10 +1686,10 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1703,10 +1697,10 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1714,10 +1708,10 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1749,8 +1743,8 @@
       <c r="A2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
-        <v>15</v>
+      <c r="B2" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -1760,8 +1754,8 @@
       <c r="A3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
-        <v>16</v>
+      <c r="B3" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -1772,10 +1766,10 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1783,10 +1777,10 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1794,10 +1788,10 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1805,10 +1799,10 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
